--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_39.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_39.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Sessions</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>HoursSleep</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.3942525439002357</v>
+        <v>-1.751705145720583</v>
       </c>
       <c r="C2">
-        <v>-0.3171550013150467</v>
+        <v>-0.2655001224231145</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.326301891130951</v>
+        <v>0.08451115885474507</v>
       </c>
       <c r="C3">
-        <v>-0.0512847420850655</v>
+        <v>1.292530463436226</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.04221068749742173</v>
+        <v>-1.939661230299091</v>
       </c>
       <c r="C4">
-        <v>0.5937024148435188</v>
+        <v>0.534994384486092</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.07145809081174294</v>
+        <v>0.2605948729137395</v>
       </c>
       <c r="C5">
-        <v>0.7629911634539596</v>
+        <v>0.8242762664952519</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.319986588621597</v>
+        <v>1.207071253582817</v>
       </c>
       <c r="C6">
-        <v>-0.08060217047042514</v>
+        <v>0.8941268972536794</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.5869954814367359</v>
+        <v>-0.8900263694967623</v>
       </c>
       <c r="C7">
-        <v>0.5565743519505499</v>
+        <v>-1.371325178050439</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>2.142053814898761</v>
+        <v>-0.1713423039973855</v>
       </c>
       <c r="C8">
-        <v>1.500094433434705</v>
+        <v>-0.6761469089328243</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-1.237592299126224</v>
+        <v>-2.433820092771986</v>
       </c>
       <c r="C9">
-        <v>1.959358301138087</v>
+        <v>-1.797163534925838</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-1.121562702385194</v>
+        <v>1.030171146612774</v>
       </c>
       <c r="C10">
-        <v>2.349436624955282</v>
+        <v>1.182740734333299</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-2.036777366468039</v>
+        <v>0.0417333369697282</v>
       </c>
       <c r="C11">
-        <v>1.271563336495052</v>
+        <v>0.1797976292553903</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.7871705979601578</v>
+        <v>0.4588337556063255</v>
       </c>
       <c r="C12">
-        <v>-0.1189562232129478</v>
+        <v>-0.6178183649266723</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.4520631473486866</v>
+        <v>2.073099745035931</v>
       </c>
       <c r="C13">
-        <v>-0.01787534787470232</v>
+        <v>1.065997425541114</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-1.329804184902095</v>
+        <v>-0.7279792444908113</v>
       </c>
       <c r="C14">
-        <v>1.08826714574329</v>
+        <v>-0.482517688356356</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.06185461775904072</v>
+        <v>-1.716519978408542</v>
       </c>
       <c r="C15">
-        <v>0.3186899537675346</v>
+        <v>0.3473150136525558</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.22333683125079</v>
+        <v>-1.984443754731824</v>
       </c>
       <c r="C16">
-        <v>1.105680444729052</v>
+        <v>-1.038638748794124</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.4601871999729911</v>
+        <v>-0.7697478703145711</v>
       </c>
       <c r="C17">
-        <v>0.2424624251098449</v>
+        <v>-2.11382686917695</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.8716180543907576</v>
+        <v>-1.22791542791244</v>
       </c>
       <c r="C18">
-        <v>-2.124696835861299</v>
+        <v>-1.550898712388755</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.4506508972206645</v>
+        <v>-0.1156021149147599</v>
       </c>
       <c r="C19">
-        <v>0.1520834841205048</v>
+        <v>-0.09962311833236512</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.7251686756498384</v>
+        <v>0.288470698764209</v>
       </c>
       <c r="C20">
-        <v>0.378692957157125</v>
+        <v>0.7767755717413891</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.0698120643385972</v>
+        <v>-1.844200812006189</v>
       </c>
       <c r="C21">
-        <v>-0.4677497284838558</v>
+        <v>-1.132784109225785</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.088678967962103</v>
+        <v>0.01167928387530817</v>
       </c>
       <c r="C22">
-        <v>1.041134267015781</v>
+        <v>-1.779897579500521</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.4223169078971145</v>
+        <v>0.5325845695577095</v>
       </c>
       <c r="C23">
-        <v>-1.223342723524824</v>
+        <v>0.5752283206776331</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.5080856052184607</v>
+        <v>1.139045262606489</v>
       </c>
       <c r="C24">
-        <v>-2.076916542587287</v>
+        <v>2.27285000746722</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.2749217314879767</v>
+        <v>0.9547952979604197</v>
       </c>
       <c r="C25">
-        <v>0.03908891631276808</v>
+        <v>1.206400201179664</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.3741423353242389</v>
+        <v>0.6475658575044932</v>
       </c>
       <c r="C26">
-        <v>-0.7934405325812468</v>
+        <v>0.6782971040254183</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.050728596227949</v>
+        <v>2.046346551224067</v>
       </c>
       <c r="C27">
-        <v>0.2292065473802296</v>
+        <v>1.200098956867962</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.8346102466475293</v>
+        <v>-0.9773553624492172</v>
       </c>
       <c r="C28">
-        <v>0.6643105791613169</v>
+        <v>0.5429855608078871</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.7520044205472068</v>
+        <v>0.02540441656201562</v>
       </c>
       <c r="C29">
-        <v>1.571937699263131</v>
+        <v>0.088606658942504</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.8694731856591082</v>
+        <v>-0.2183137265512543</v>
       </c>
       <c r="C30">
-        <v>0.6323808252902203</v>
+        <v>0.9654758930649027</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.544796244775162</v>
+        <v>-1.250651232498229</v>
       </c>
       <c r="C31">
-        <v>-2.42407051433022</v>
+        <v>0.07660365783366352</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-2.035993107941971</v>
+        <v>0.4058427628428087</v>
       </c>
       <c r="C32">
-        <v>0.7629754651833102</v>
+        <v>0.02730778369831702</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>2.383601115148642</v>
+        <v>1.034721029775536</v>
       </c>
       <c r="C33">
-        <v>0.5964995537051794</v>
+        <v>1.454701470959552</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.7669806885046454</v>
+        <v>0.8613516944869576</v>
       </c>
       <c r="C34">
-        <v>-0.2303734698790025</v>
+        <v>0.7039765072382098</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.542967585417609</v>
+        <v>-1.243573377743538</v>
       </c>
       <c r="C35">
-        <v>1.479482763803735</v>
+        <v>0.6919120923298219</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.360212709029817</v>
+        <v>1.651903287419753</v>
       </c>
       <c r="C36">
-        <v>1.071168872394421</v>
+        <v>1.130967098769366</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.5335458303434257</v>
+        <v>-0.07028536097134325</v>
       </c>
       <c r="C37">
-        <v>0.7005127329435608</v>
+        <v>-0.4892179925778662</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.7852690596628447</v>
+        <v>0.5513772386395732</v>
       </c>
       <c r="C38">
-        <v>-0.3010432263624272</v>
+        <v>-0.01344155863266736</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.5540189719162022</v>
+        <v>-0.1590545647152793</v>
       </c>
       <c r="C39">
-        <v>0.2076295565006405</v>
+        <v>0.7028578054607075</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.2364314931236702</v>
+        <v>0.6463819117963133</v>
       </c>
       <c r="C40">
-        <v>-0.3850428807390471</v>
+        <v>-0.7056256695284426</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.8446249967224363</v>
+        <v>0.04636129351722803</v>
       </c>
       <c r="C41">
-        <v>-0.2748021483976359</v>
+        <v>-1.417173349999652</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.3033372990785228</v>
+        <v>-0.1352218138094143</v>
       </c>
       <c r="C42">
-        <v>-0.1420945770754571</v>
+        <v>-1.471807459644184</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.09537441433437009</v>
+        <v>0.7855686231671699</v>
       </c>
       <c r="C43">
-        <v>-0.1894427237018059</v>
+        <v>0.6983410136449431</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.297840704166713</v>
+        <v>0.3726134483209004</v>
       </c>
       <c r="C44">
-        <v>-1.594089434635039</v>
+        <v>0.5842798865560347</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.9734365145353134</v>
+        <v>1.301393413297266</v>
       </c>
       <c r="C45">
-        <v>-0.6870528619828289</v>
+        <v>0.4267634412603315</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.059367406666668</v>
+        <v>0.9501716462557092</v>
       </c>
       <c r="C46">
-        <v>1.702144388458015</v>
+        <v>0.2356266622489624</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.3815772517876225</v>
+        <v>0.6660519042090584</v>
       </c>
       <c r="C47">
-        <v>0.2879460706628709</v>
+        <v>0.4598967934713847</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.3719819978055669</v>
+        <v>-1.590491721025074</v>
       </c>
       <c r="C48">
-        <v>-1.110409631880009</v>
+        <v>-0.3634667186308901</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.7238352858631533</v>
+        <v>-1.012449989833154</v>
       </c>
       <c r="C49">
-        <v>0.8608634092898449</v>
+        <v>-0.7608070005706117</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.1132155537450674</v>
+        <v>-1.709551236086982</v>
       </c>
       <c r="C50">
-        <v>1.068350541783203</v>
+        <v>-1.301536494038759</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.5595591488743058</v>
+        <v>0.4723782384456174</v>
       </c>
       <c r="C51">
-        <v>0.669693494083065</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-1.487224861280741</v>
-      </c>
-      <c r="C52">
-        <v>-0.002084939427851817</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>0.873888473067186</v>
-      </c>
-      <c r="C53">
-        <v>-0.2492534963989227</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>1.131855762848846</v>
-      </c>
-      <c r="C54">
-        <v>-0.1845528191632293</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>0.3280948732009649</v>
-      </c>
-      <c r="C55">
-        <v>1.745727388269248</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>-1.284121460977421</v>
-      </c>
-      <c r="C56">
-        <v>-0.4534687726033413</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>-1.675751259636383</v>
-      </c>
-      <c r="C57">
-        <v>1.033140733797552</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>0.69908454142052</v>
-      </c>
-      <c r="C58">
-        <v>0.5347471394402632</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>-0.8400145019443861</v>
-      </c>
-      <c r="C59">
-        <v>0.3914221120978441</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>1.545469767875791</v>
-      </c>
-      <c r="C60">
-        <v>-1.512248789825123</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>0.5043531889010437</v>
-      </c>
-      <c r="C61">
-        <v>0.06756559811421134</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>1.159683161056091</v>
-      </c>
-      <c r="C62">
-        <v>0.6554038678115963</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>-0.07095466253979531</v>
-      </c>
-      <c r="C63">
-        <v>-0.8458014953196717</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>-0.6944034415652719</v>
-      </c>
-      <c r="C64">
-        <v>-2.028492767272597</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>0.04069924629972124</v>
-      </c>
-      <c r="C65">
-        <v>0.4413101375398297</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>0.708330102827376</v>
-      </c>
-      <c r="C66">
-        <v>0.3368870681149423</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>-1.365125972828302</v>
-      </c>
-      <c r="C67">
-        <v>1.451588605081568</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>0.1849243165056522</v>
-      </c>
-      <c r="C68">
-        <v>0.1081086854137836</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>0.8960221150171066</v>
-      </c>
-      <c r="C69">
-        <v>0.3475057189297907</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>0.262216442478519</v>
-      </c>
-      <c r="C70">
-        <v>1.894789521546728</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-0.5161915075034783</v>
-      </c>
-      <c r="C71">
-        <v>-0.865670130209049</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>0.501921361666942</v>
-      </c>
-      <c r="C72">
-        <v>1.103587568761174</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>0.4635334157076165</v>
-      </c>
-      <c r="C73">
-        <v>-0.738095210685205</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>0.3376469242023853</v>
-      </c>
-      <c r="C74">
-        <v>-0.1136689995247236</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-0.6756056107969279</v>
-      </c>
-      <c r="C75">
-        <v>0.4231315660750637</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>-2.319497892942382</v>
-      </c>
-      <c r="C76">
-        <v>-0.005408396495152568</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-0.6634336247500694</v>
-      </c>
-      <c r="C77">
-        <v>0.5549312471538337</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>1.246350746956374</v>
-      </c>
-      <c r="C78">
-        <v>-0.4204403997887201</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>-2.219873645293408</v>
-      </c>
-      <c r="C79">
-        <v>0.3411319552581693</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>0.3324188602965196</v>
-      </c>
-      <c r="C80">
-        <v>0.3801170617252878</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>0.3879594327616226</v>
-      </c>
-      <c r="C81">
-        <v>0.4888126812007775</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>0.977969018484204</v>
-      </c>
-      <c r="C82">
-        <v>-0.4662848072196508</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>0.8760899479750576</v>
-      </c>
-      <c r="C83">
-        <v>-0.1417392971058953</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>0.5711162828855988</v>
-      </c>
-      <c r="C84">
-        <v>0.4848561190877088</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-1.179049786435206</v>
-      </c>
-      <c r="C85">
-        <v>-0.3378637527484845</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-0.9638608532064837</v>
-      </c>
-      <c r="C86">
-        <v>0.243043221547261</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>-2.354602838109043</v>
-      </c>
-      <c r="C87">
-        <v>0.1301232964364862</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>0.7815968046590535</v>
-      </c>
-      <c r="C88">
-        <v>-0.05491527688367837</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>0.8341220389483711</v>
-      </c>
-      <c r="C89">
-        <v>0.2138601180944332</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-1.397704668397653</v>
-      </c>
-      <c r="C90">
-        <v>1.175804184107095</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-0.8302364302880409</v>
-      </c>
-      <c r="C91">
-        <v>0.4624506985614588</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>0.9991619764054631</v>
-      </c>
-      <c r="C92">
-        <v>0.7037543831404076</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>-1.227596037110626</v>
-      </c>
-      <c r="C93">
-        <v>-1.421191676418711</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>-0.6495361668550107</v>
-      </c>
-      <c r="C94">
-        <v>-0.04107529617564604</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>-0.4265440432031002</v>
-      </c>
-      <c r="C95">
-        <v>0.09171285438860298</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>0.373784943923201</v>
-      </c>
-      <c r="C96">
-        <v>0.3499133776466601</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>-0.5463596181317593</v>
-      </c>
-      <c r="C97">
-        <v>-0.591731711900372</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>0.8023054460134967</v>
-      </c>
-      <c r="C98">
-        <v>0.5009231368690895</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>-0.4619593381379918</v>
-      </c>
-      <c r="C99">
-        <v>0.3332889969910767</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>-1.19838544203073</v>
-      </c>
-      <c r="C100">
-        <v>2.371273313045339</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>-0.06255508496597885</v>
-      </c>
-      <c r="C101">
-        <v>-0.7156638275055041</v>
+        <v>0.4955808134787857</v>
       </c>
     </row>
   </sheetData>
